--- a/backend/apps/cotizador/templates/PLANTILLA_FACTURA.xlsx
+++ b/backend/apps/cotizador/templates/PLANTILLA_FACTURA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas P&amp;M\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sistemas_pm\Proyectos\Sistema-Integral-de-Gestion\backend\apps\cotizador\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC1A6C6F-5DB2-4D07-9306-FD3729132F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A46854-7EB5-4AFE-A3B9-38CA8AC46971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="784" firstSheet="7" activeTab="7" xr2:uid="{6B8609C1-1617-49BD-9344-1A1A9DA0D237}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9960" tabRatio="784" firstSheet="7" activeTab="7" xr2:uid="{6B8609C1-1617-49BD-9344-1A1A9DA0D237}"/>
   </bookViews>
   <sheets>
     <sheet name="Forma_Pago" sheetId="4" state="hidden" r:id="rId1"/>
@@ -1893,10 +1893,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="193" formatCode="0.0"/>
-    <numFmt numFmtId="201" formatCode="0.0000"/>
-    <numFmt numFmtId="202" formatCode="000"/>
-    <numFmt numFmtId="203" formatCode="00"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="000"/>
+    <numFmt numFmtId="167" formatCode="00"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -2418,18 +2418,18 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2438,16 +2438,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="193" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2455,25 +2454,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="202" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2484,7 +2472,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="203" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2502,30 +2490,18 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="202" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2534,14 +2510,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="202" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2554,10 +2524,10 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2566,13 +2536,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="202" fontId="4" fillId="0" borderId="8" xfId="5" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="5" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2581,34 +2551,34 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="202" fontId="4" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="193" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="203" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="203" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2620,22 +2590,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="201" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2653,21 +2623,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2677,7 +2638,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2694,7 +2655,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2702,11 +2663,8 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2716,16 +2674,10 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="15" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2742,7 +2694,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2751,25 +2769,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2795,75 +2807,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -3284,37 +3227,36 @@
   <dimension ref="A2:P36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="34.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="11" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="11" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="0" style="11" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="26" style="11" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="11" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="11" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="47.44140625" style="11" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="11" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="88.6640625" style="11" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="18.44140625" style="11" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" style="11" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="11"/>
-    <col min="16" max="16" width="57.44140625" style="11" customWidth="1"/>
-    <col min="17" max="17" width="11.44140625" style="11"/>
-    <col min="18" max="18" width="48.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="26.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="34.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="10" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="10" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="0" style="10" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="26" style="10" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="10" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="10" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="47.44140625" style="10" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="10" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="88.6640625" style="10" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" style="10" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="10" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="10"/>
+    <col min="16" max="16" width="57.44140625" style="10" customWidth="1"/>
+    <col min="17" max="17" width="11.44140625" style="10"/>
+    <col min="18" max="18" width="48.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="123"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="127"/>
     </row>
     <row r="3" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -3324,9 +3266,8 @@
         <v>30</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -3336,63 +3277,58 @@
         <v>0</v>
       </c>
       <c r="E4" s="9"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="26" t="s">
+      <c r="I6" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="26" t="s">
+      <c r="J6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="26" t="s">
+      <c r="K6" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="20" t="s">
         <v>69</v>
       </c>
       <c r="M6" s="6" t="s">
@@ -3403,1037 +3339,1037 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="21">
         <v>1</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="30" t="str">
+      <c r="E7" s="24" t="str">
         <f>IF(C7="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="F7" s="30" t="str">
+      <c r="F7" s="24" t="str">
         <f>IF(C7="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="30" t="str">
+      <c r="H7" s="24" t="str">
         <f>IF(C7="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="I7" s="30" t="str">
+      <c r="I7" s="24" t="str">
         <f>IF(A7="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="30" t="str">
+      <c r="K7" s="24" t="str">
         <f>IF(C7="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="L7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="26">
         <v>42736</v>
       </c>
-      <c r="N7" s="33"/>
-      <c r="P7" s="81" t="s">
+      <c r="N7" s="27"/>
+      <c r="P7" s="69" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+      <c r="A8" s="21">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="M8" s="37">
+      <c r="M8" s="28">
         <v>42736</v>
       </c>
-      <c r="N8" s="38"/>
-      <c r="P8" s="81" t="s">
+      <c r="N8" s="29"/>
+      <c r="P8" s="69" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="21">
         <v>3</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="L9" s="36" t="s">
+      <c r="L9" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="M9" s="37">
+      <c r="M9" s="28">
         <v>42736</v>
       </c>
-      <c r="N9" s="38"/>
-      <c r="P9" s="81" t="s">
+      <c r="N9" s="29"/>
+      <c r="P9" s="69" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="A10" s="21">
         <v>4</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L10" s="36" t="s">
+      <c r="L10" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="37">
+      <c r="M10" s="28">
         <v>42736</v>
       </c>
-      <c r="N10" s="38"/>
-      <c r="P10" s="81" t="s">
+      <c r="N10" s="29"/>
+      <c r="P10" s="69" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
+      <c r="A11" s="21">
         <v>5</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="35" t="s">
+      <c r="H11" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="35" t="s">
+      <c r="J11" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="36" t="s">
+      <c r="L11" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M11" s="37">
+      <c r="M11" s="28">
         <v>42736</v>
       </c>
-      <c r="N11" s="38"/>
-      <c r="P11" s="81" t="s">
+      <c r="N11" s="29"/>
+      <c r="P11" s="69" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
+      <c r="A12" s="21">
         <v>6</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="35" t="s">
+      <c r="I12" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K12" s="35" t="s">
+      <c r="K12" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="36" t="s">
+      <c r="L12" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="37">
+      <c r="M12" s="28">
         <v>42736</v>
       </c>
-      <c r="N12" s="38"/>
-      <c r="P12" s="81" t="s">
+      <c r="N12" s="29"/>
+      <c r="P12" s="69" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
+      <c r="A13" s="21">
         <v>8</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="30" t="str">
+      <c r="E13" s="24" t="str">
         <f>IF(C13="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="F13" s="30" t="str">
+      <c r="F13" s="24" t="str">
         <f>IF(C13="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="35" t="str">
+      <c r="H13" s="24" t="str">
         <f>IF(C13="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="I13" s="35" t="str">
+      <c r="I13" s="24" t="str">
         <f>IF(A13="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K13" s="30" t="str">
+      <c r="K13" s="24" t="str">
         <f>IF(C13="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="L13" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M13" s="37">
+      <c r="M13" s="28">
         <v>42736</v>
       </c>
-      <c r="N13" s="38"/>
-      <c r="P13" s="81" t="s">
+      <c r="N13" s="29"/>
+      <c r="P13" s="69" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="40">
+      <c r="A14" s="31">
         <v>12</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="30" t="str">
+      <c r="E14" s="24" t="str">
         <f t="shared" ref="E14:E23" si="0">IF(C14="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="F14" s="30" t="str">
+      <c r="F14" s="24" t="str">
         <f t="shared" ref="F14:F23" si="1">IF(C14="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H14" s="35" t="str">
+      <c r="H14" s="24" t="str">
         <f t="shared" ref="H14:H23" si="2">IF(C14="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="I14" s="35" t="str">
+      <c r="I14" s="24" t="str">
         <f t="shared" ref="I14:I23" si="3">IF(A14="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="J14" s="35" t="s">
+      <c r="J14" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="30" t="str">
+      <c r="K14" s="24" t="str">
         <f t="shared" ref="K14:K23" si="4">IF(C14="Sí","Sí","No")</f>
         <v>No</v>
       </c>
-      <c r="L14" s="31" t="s">
+      <c r="L14" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="28">
         <v>42736</v>
       </c>
-      <c r="N14" s="38"/>
-      <c r="P14" s="81" t="s">
+      <c r="N14" s="29"/>
+      <c r="P14" s="69" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="40">
+      <c r="A15" s="31">
         <v>13</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="30" t="str">
+      <c r="E15" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F15" s="30" t="str">
+      <c r="F15" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="35" t="str">
+      <c r="H15" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I15" s="35" t="str">
+      <c r="I15" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K15" s="30" t="str">
+      <c r="K15" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L15" s="31" t="s">
+      <c r="L15" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="28">
         <v>42736</v>
       </c>
-      <c r="N15" s="38"/>
-      <c r="P15" s="81" t="s">
+      <c r="N15" s="29"/>
+      <c r="P15" s="69" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="40">
+      <c r="A16" s="31">
         <v>14</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="30" t="str">
+      <c r="E16" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F16" s="30" t="str">
+      <c r="F16" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="35" t="str">
+      <c r="H16" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I16" s="35" t="str">
+      <c r="I16" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K16" s="30" t="str">
+      <c r="K16" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L16" s="31" t="s">
+      <c r="L16" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="37">
+      <c r="M16" s="28">
         <v>42736</v>
       </c>
-      <c r="N16" s="38"/>
-      <c r="P16" s="81" t="s">
+      <c r="N16" s="29"/>
+      <c r="P16" s="69" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="40">
+      <c r="A17" s="31">
         <v>15</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="30" t="str">
+      <c r="E17" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F17" s="30" t="str">
+      <c r="F17" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="G17" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="35" t="str">
+      <c r="H17" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I17" s="35" t="str">
+      <c r="I17" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K17" s="30" t="str">
+      <c r="K17" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L17" s="31" t="s">
+      <c r="L17" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M17" s="37">
+      <c r="M17" s="28">
         <v>42736</v>
       </c>
-      <c r="N17" s="38"/>
-      <c r="P17" s="81" t="s">
+      <c r="N17" s="29"/>
+      <c r="P17" s="69" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="40">
+      <c r="A18" s="31">
         <v>17</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="30" t="str">
+      <c r="E18" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F18" s="30" t="str">
+      <c r="F18" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H18" s="35" t="str">
+      <c r="H18" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I18" s="35" t="str">
+      <c r="I18" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J18" s="35" t="s">
+      <c r="J18" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K18" s="30" t="str">
+      <c r="K18" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L18" s="31" t="s">
+      <c r="L18" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="28">
         <v>42736</v>
       </c>
-      <c r="N18" s="38"/>
-      <c r="P18" s="81" t="s">
+      <c r="N18" s="29"/>
+      <c r="P18" s="69" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="40">
+      <c r="A19" s="31">
         <v>23</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="30" t="str">
+      <c r="E19" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F19" s="30" t="str">
+      <c r="F19" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="35" t="str">
+      <c r="H19" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I19" s="35" t="str">
+      <c r="I19" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K19" s="30" t="str">
+      <c r="K19" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L19" s="31" t="s">
+      <c r="L19" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="28">
         <v>42736</v>
       </c>
-      <c r="N19" s="38"/>
-      <c r="P19" s="81" t="s">
+      <c r="N19" s="29"/>
+      <c r="P19" s="69" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="40">
+      <c r="A20" s="31">
         <v>24</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="30" t="str">
+      <c r="E20" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F20" s="30" t="str">
+      <c r="F20" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="35" t="str">
+      <c r="H20" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I20" s="35" t="str">
+      <c r="I20" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K20" s="30" t="str">
+      <c r="K20" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L20" s="31" t="s">
+      <c r="L20" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M20" s="37">
+      <c r="M20" s="28">
         <v>42736</v>
       </c>
-      <c r="N20" s="38"/>
-      <c r="P20" s="81" t="s">
+      <c r="N20" s="29"/>
+      <c r="P20" s="69" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="40">
+      <c r="A21" s="31">
         <v>25</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="30" t="str">
+      <c r="E21" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F21" s="30" t="str">
+      <c r="F21" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="35" t="str">
+      <c r="H21" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I21" s="35" t="str">
+      <c r="I21" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K21" s="30" t="str">
+      <c r="K21" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L21" s="31" t="s">
+      <c r="L21" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="28">
         <v>42736</v>
       </c>
-      <c r="N21" s="38"/>
-      <c r="P21" s="81" t="s">
+      <c r="N21" s="29"/>
+      <c r="P21" s="69" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="40">
+      <c r="A22" s="31">
         <v>26</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="30" t="str">
+      <c r="E22" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F22" s="30" t="str">
+      <c r="F22" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="35" t="str">
+      <c r="H22" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I22" s="35" t="str">
+      <c r="I22" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K22" s="30" t="str">
+      <c r="K22" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L22" s="31" t="s">
+      <c r="L22" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="37">
+      <c r="M22" s="28">
         <v>42736</v>
       </c>
-      <c r="N22" s="38"/>
-      <c r="P22" s="81" t="s">
+      <c r="N22" s="29"/>
+      <c r="P22" s="69" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="40">
+      <c r="A23" s="31">
         <v>27</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="30" t="str">
+      <c r="E23" s="24" t="str">
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="F23" s="30" t="str">
+      <c r="F23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>No</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="35" t="str">
+      <c r="H23" s="24" t="str">
         <f t="shared" si="2"/>
         <v>No</v>
       </c>
-      <c r="I23" s="35" t="str">
+      <c r="I23" s="24" t="str">
         <f t="shared" si="3"/>
         <v>No</v>
       </c>
-      <c r="J23" s="35" t="s">
+      <c r="J23" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K23" s="30" t="str">
+      <c r="K23" s="24" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="L23" s="31" t="s">
+      <c r="L23" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="28">
         <v>42736</v>
       </c>
-      <c r="N23" s="38"/>
-      <c r="P23" s="81" t="s">
+      <c r="N23" s="29"/>
+      <c r="P23" s="69" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="40">
+      <c r="A24" s="31">
         <v>28</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L24" s="36" t="s">
+      <c r="L24" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="M24" s="37">
+      <c r="M24" s="28">
         <v>42736</v>
       </c>
-      <c r="N24" s="38"/>
-      <c r="P24" s="81" t="s">
+      <c r="N24" s="29"/>
+      <c r="P24" s="69" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="40">
+      <c r="A25" s="31">
         <v>29</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I25" s="35" t="s">
+      <c r="I25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J25" s="35" t="s">
+      <c r="J25" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="K25" s="35" t="s">
+      <c r="K25" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="36" t="s">
+      <c r="L25" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="28">
         <v>42736</v>
       </c>
-      <c r="N25" s="38"/>
-      <c r="P25" s="81" t="s">
+      <c r="N25" s="29"/>
+      <c r="P25" s="69" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="40">
+      <c r="A26" s="31">
         <v>30</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I26" s="35" t="s">
+      <c r="I26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K26" s="35" t="s">
+      <c r="K26" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="L26" s="42" t="s">
+      <c r="L26" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="M26" s="37">
+      <c r="M26" s="28">
         <v>42943</v>
       </c>
-      <c r="N26" s="38"/>
-      <c r="P26" s="81" t="s">
+      <c r="N26" s="29"/>
+      <c r="P26" s="69" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="40">
+      <c r="A27" s="31">
         <v>99</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="34" t="s">
+      <c r="G27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="H27" s="34" t="s">
+      <c r="H27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="J27" s="34" t="s">
+      <c r="J27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="L27" s="28" t="s">
+      <c r="L27" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="28">
         <v>42736</v>
       </c>
-      <c r="N27" s="38"/>
-      <c r="P27" s="81" t="s">
+      <c r="N27" s="29"/>
+      <c r="P27" s="69" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
+      <c r="A29" s="34"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
+      <c r="A30" s="34"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="44"/>
+      <c r="A31" s="34"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
+      <c r="A32" s="34"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
+      <c r="A33" s="34"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
+      <c r="A34" s="34"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="44"/>
+      <c r="A35" s="34"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
+      <c r="A36" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4450,20 +4386,20 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26" style="13" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" style="11" customWidth="1"/>
-    <col min="3" max="4" width="11.44140625" style="11"/>
-    <col min="5" max="5" width="22.44140625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="17" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="26" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" style="10" customWidth="1"/>
+    <col min="3" max="4" width="11.44140625" style="10"/>
+    <col min="5" max="5" width="22.44140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="17" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
     </row>
     <row r="2" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4480,10 +4416,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+      <c r="A3" s="26">
         <v>42736</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="7">
         <v>1</v>
       </c>
@@ -4493,82 +4429,82 @@
     </row>
     <row r="4" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="20" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="46">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="47"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="46">
+      <c r="A7" s="36">
         <v>2</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="47"/>
-      <c r="H7" s="11" t="s">
+      <c r="F7" s="30"/>
+      <c r="H7" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="46">
+      <c r="A8" s="36">
         <v>3</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="F8" s="47"/>
-      <c r="H8" s="11" t="s">
+      <c r="F8" s="30"/>
+      <c r="H8" s="10" t="s">
         <v>582</v>
       </c>
     </row>
@@ -4586,20 +4522,20 @@
   <dimension ref="A2:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19" style="11" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="11"/>
-    <col min="6" max="6" width="38.6640625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="28.88671875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="19" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="10"/>
+    <col min="6" max="6" width="38.6640625" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="125" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="121"/>
+      <c r="B2" s="125"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -4619,10 +4555,10 @@
     </row>
     <row r="5" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="37" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -4633,32 +4569,32 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="26">
         <v>42736</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="F7" s="80" t="s">
+      <c r="D7" s="27"/>
+      <c r="F7" s="68" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="38">
         <v>42736</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="F8" s="80" t="s">
+      <c r="D8" s="24"/>
+      <c r="F8" s="68" t="s">
         <v>560</v>
       </c>
     </row>
@@ -4676,22 +4612,22 @@
   <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" style="11" customWidth="1"/>
-    <col min="2" max="2" width="97.33203125" style="51" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="11"/>
-    <col min="6" max="6" width="23.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.44140625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="32.88671875" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="25" style="10" customWidth="1"/>
+    <col min="2" max="2" width="97.33203125" style="39" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="10"/>
+    <col min="6" max="6" width="23.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.44140625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="32.88671875" style="10" customWidth="1"/>
+    <col min="9" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="128" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="125"/>
+      <c r="B1" s="128"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4708,10 +4644,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+      <c r="A3" s="26">
         <v>42736</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="7">
         <v>1</v>
       </c>
@@ -4721,2510 +4657,2510 @@
     </row>
     <row r="4" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="40" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="55">
+      <c r="C6" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="43">
         <v>0.35274244523672377</v>
       </c>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="67" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="55">
-        <v>0.35274244523672382</v>
-      </c>
-      <c r="F7" s="79" t="s">
+      <c r="C7" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="43">
+        <v>0.35274244523672382</v>
+      </c>
+      <c r="F7" s="67" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="55">
+      <c r="C8" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="55">
+      <c r="C9" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="55">
+      <c r="C10" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="55">
+      <c r="C11" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="55">
+      <c r="C12" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="43">
         <v>0.62972177265132079</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="55">
+      <c r="C13" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="43">
         <v>0.43690120915914099</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="55">
+      <c r="C14" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="55">
+      <c r="C15" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="C16" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="55">
+      <c r="C16" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="55">
+      <c r="C17" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="55">
+      <c r="C18" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" s="55">
+      <c r="C19" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="55">
+      <c r="C22" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="55">
+      <c r="C23" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" s="55">
+      <c r="C24" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="43">
         <v>0.35362525884932122</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="55">
+      <c r="C25" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="55">
+      <c r="C26" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="43">
         <v>0.50955645199952782</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="55">
+      <c r="C27" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="C28" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="55">
+      <c r="C28" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="C29" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="55">
+      <c r="C29" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="55">
+      <c r="C31" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="43">
         <v>0.36297996001621324</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" s="55">
+      <c r="C32" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="43">
         <v>0.31494390158765018</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="55">
+      <c r="C33" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="C34" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="55">
+      <c r="C34" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="C35" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" s="55">
+      <c r="C35" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="43">
         <v>0.49467011705409375</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="C36" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" s="55">
+      <c r="C36" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C37" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="C38" s="53" t="s">
+      <c r="C38" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="43">
         <v>0.44678677950242945</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="C39" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" s="55">
+      <c r="C39" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="43">
         <v>0.27756484599582842</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="42" t="s">
         <v>195</v>
       </c>
-      <c r="C40" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D40" s="55">
+      <c r="C40" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="43">
         <v>0.33224855773433476</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="C41" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="55">
+      <c r="C41" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="C42" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="55">
+      <c r="C42" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="43">
         <v>0.31195931980170266</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="53" t="s">
+      <c r="A43" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D43" s="55">
+      <c r="C43" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
+      <c r="A44" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="C44" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D44" s="55">
+      <c r="C44" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44" s="43">
         <v>0.36297996001621352</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="B45" s="54" t="s">
+      <c r="B45" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="C45" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" s="55">
+      <c r="C45" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="55">
+      <c r="C46" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="43">
         <v>0.41633417566741715</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="C47" s="53" t="s">
+      <c r="C47" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="55">
+      <c r="D47" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
+      <c r="A48" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="C48" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48" s="55">
+      <c r="C48" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" s="43">
         <v>0.39875072822218555</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="53" t="s">
+      <c r="A49" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="C49" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D49" s="55">
+      <c r="C49" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="43">
         <v>0.50807896142007469</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="53" t="s">
+      <c r="A50" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="C50" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" s="55">
+      <c r="C50" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="43">
         <v>0.3032625980729155</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
+      <c r="A51" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="B51" s="54" t="s">
+      <c r="B51" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="C51" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" s="55">
+      <c r="C51" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="43">
         <v>0.34049227228456863</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="53" t="s">
+      <c r="A52" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="B52" s="54" t="s">
+      <c r="B52" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="C52" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="55">
+      <c r="C52" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="53" t="s">
+      <c r="A53" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="B53" s="54" t="s">
+      <c r="B53" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="C53" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" s="55">
+      <c r="C53" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="53" t="s">
+      <c r="A54" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="B54" s="54" t="s">
+      <c r="B54" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="C54" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="55">
+      <c r="C54" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="43">
         <v>0.39672087279238971</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="53" t="s">
+      <c r="A55" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="C55" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="55">
+      <c r="C55" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="43">
         <v>0.35464369114761268</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="53" t="s">
+      <c r="A56" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="B56" s="54" t="s">
+      <c r="B56" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="C56" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" s="55">
+      <c r="C56" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="53" t="s">
+      <c r="A57" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="B57" s="54" t="s">
+      <c r="B57" s="42" t="s">
         <v>228</v>
       </c>
-      <c r="C57" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="55">
+      <c r="C57" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="43">
         <v>0.2879697170616744</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="53" t="s">
+      <c r="A58" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="B58" s="54" t="s">
+      <c r="B58" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="C58" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D58" s="55">
+      <c r="C58" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
+      <c r="A59" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="54" t="s">
+      <c r="B59" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="C59" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D59" s="55">
+      <c r="C59" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="53" t="s">
+      <c r="A60" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="B60" s="54" t="s">
+      <c r="B60" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="C60" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D60" s="55">
+      <c r="C60" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="53" t="s">
+      <c r="A61" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="B61" s="54" t="s">
+      <c r="B61" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="C61" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="55">
+      <c r="C61" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="53" t="s">
+      <c r="A62" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="B62" s="54" t="s">
+      <c r="B62" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="C62" s="53" t="s">
+      <c r="C62" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D62" s="55">
+      <c r="D62" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="53" t="s">
+      <c r="A63" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="B63" s="54" t="s">
+      <c r="B63" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C63" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="55">
+      <c r="C63" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" s="43">
         <v>0.35653159361198999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="53" t="s">
+      <c r="A64" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="B64" s="54" t="s">
+      <c r="B64" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="C64" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D64" s="55">
+      <c r="C64" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" s="43">
         <v>0.35178505274708649</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="53" t="s">
+      <c r="A65" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="B65" s="54" t="s">
+      <c r="B65" s="42" t="s">
         <v>243</v>
       </c>
-      <c r="C65" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D65" s="55">
+      <c r="C65" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D65" s="43">
         <v>0.35316196530037297</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="53" t="s">
+      <c r="A66" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="C66" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66" s="55">
+      <c r="C66" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D66" s="43">
         <v>0.27641922337373315</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="53" t="s">
+      <c r="A67" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="42" t="s">
         <v>247</v>
       </c>
-      <c r="C67" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D67" s="55">
+      <c r="C67" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="53" t="s">
+      <c r="A68" s="41" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="54" t="s">
+      <c r="B68" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" s="55">
+      <c r="C68" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="53" t="s">
+      <c r="A69" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="B69" s="54" t="s">
+      <c r="B69" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="C69" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D69" s="55">
+      <c r="C69" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D69" s="43">
         <v>0.37590579047445571</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="53" t="s">
+      <c r="A70" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="B70" s="54" t="s">
+      <c r="B70" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="C70" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D70" s="55">
+      <c r="C70" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D70" s="43">
         <v>0.34778625564600507</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="53" t="s">
+      <c r="A71" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="B71" s="54" t="s">
+      <c r="B71" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="C71" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D71" s="55">
+      <c r="C71" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D71" s="43">
         <v>0.33058245619240545</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="53" t="s">
+      <c r="A72" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="C72" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D72" s="55">
+      <c r="C72" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D72" s="43">
         <v>0.2953978508154147</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="53" t="s">
+      <c r="A73" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="B73" s="54" t="s">
+      <c r="B73" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="C73" s="53" t="s">
+      <c r="C73" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="55">
+      <c r="D73" s="43">
         <v>0.58608926530886629</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="53" t="s">
+      <c r="A74" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="B74" s="54" t="s">
+      <c r="B74" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="C74" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D74" s="55">
+      <c r="C74" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D74" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="53" t="s">
+      <c r="A75" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="B75" s="54" t="s">
+      <c r="B75" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="C75" s="53" t="s">
+      <c r="C75" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D75" s="55">
+      <c r="D75" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="53" t="s">
+      <c r="A76" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="B76" s="54" t="s">
+      <c r="B76" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="C76" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D76" s="55">
+      <c r="C76" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D76" s="43">
         <v>0.28100194698217756</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="53" t="s">
+      <c r="A77" s="41" t="s">
         <v>266</v>
       </c>
-      <c r="B77" s="54" t="s">
+      <c r="B77" s="42" t="s">
         <v>267</v>
       </c>
-      <c r="C77" s="53" t="s">
+      <c r="C77" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D77" s="55">
+      <c r="D77" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="53" t="s">
+      <c r="A78" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="B78" s="54" t="s">
+      <c r="B78" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="C78" s="53" t="s">
+      <c r="C78" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="55">
+      <c r="D78" s="43">
         <v>0.57268230383254815</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="53" t="s">
+      <c r="A79" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="B79" s="54" t="s">
+      <c r="B79" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="C79" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D79" s="55">
+      <c r="C79" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D79" s="43">
         <v>0.30213624241311149</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="53" t="s">
+      <c r="A80" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B80" s="54" t="s">
+      <c r="B80" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="C80" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D80" s="55">
+      <c r="C80" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D80" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="53" t="s">
+      <c r="A81" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="B81" s="54" t="s">
+      <c r="B81" s="42" t="s">
         <v>274</v>
       </c>
-      <c r="C81" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D81" s="55">
+      <c r="C81" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D81" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="53" t="s">
+      <c r="A82" s="41" t="s">
         <v>275</v>
       </c>
-      <c r="B82" s="54" t="s">
+      <c r="B82" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="C82" s="53" t="s">
+      <c r="C82" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D82" s="55">
+      <c r="D82" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="53" t="s">
+      <c r="A83" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="B83" s="54" t="s">
+      <c r="B83" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="C83" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D83" s="55">
+      <c r="C83" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D83" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="53" t="s">
+      <c r="A84" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="C84" s="53" t="s">
+      <c r="C84" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D84" s="55">
+      <c r="D84" s="43">
         <v>0.35376761433200371</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="53" t="s">
+      <c r="A85" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B85" s="54" t="s">
+      <c r="B85" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="C85" s="53" t="s">
+      <c r="C85" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D85" s="55">
+      <c r="D85" s="43">
         <v>0.3270606820844067</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="53" t="s">
+      <c r="A86" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="B86" s="54" t="s">
+      <c r="B86" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="C86" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D86" s="55">
+      <c r="C86" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D86" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="53" t="s">
+      <c r="A87" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="B87" s="54" t="s">
+      <c r="B87" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="C87" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D87" s="55">
+      <c r="C87" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="53" t="s">
+      <c r="A88" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B88" s="54" t="s">
+      <c r="B88" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="C88" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D88" s="55">
+      <c r="C88" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="53" t="s">
+      <c r="A89" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="B89" s="54" t="s">
+      <c r="B89" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="C89" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D89" s="55">
+      <c r="C89" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D89" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="53" t="s">
+      <c r="A90" s="41" t="s">
         <v>291</v>
       </c>
-      <c r="B90" s="54" t="s">
+      <c r="B90" s="42" t="s">
         <v>292</v>
       </c>
-      <c r="C90" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D90" s="55">
+      <c r="C90" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D90" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="53" t="s">
+      <c r="A91" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="B91" s="54" t="s">
+      <c r="B91" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="C91" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D91" s="55">
+      <c r="C91" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D91" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="53" t="s">
+      <c r="A92" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="B92" s="54" t="s">
+      <c r="B92" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="C92" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D92" s="55">
+      <c r="C92" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D92" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="53" t="s">
+      <c r="A93" s="41" t="s">
         <v>297</v>
       </c>
-      <c r="B93" s="54" t="s">
+      <c r="B93" s="42" t="s">
         <v>298</v>
       </c>
-      <c r="C93" s="53" t="s">
+      <c r="C93" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D93" s="55">
+      <c r="D93" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="53" t="s">
+      <c r="A94" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="B94" s="54" t="s">
+      <c r="B94" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="C94" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D94" s="55">
+      <c r="C94" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" s="43">
         <v>0.35881109228176644</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="53" t="s">
+      <c r="A95" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="B95" s="54" t="s">
+      <c r="B95" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="C95" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D95" s="55">
+      <c r="C95" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D95" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="53" t="s">
+      <c r="A96" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="B96" s="54" t="s">
+      <c r="B96" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="C96" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D96" s="55">
+      <c r="C96" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D96" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="53" t="s">
+      <c r="A97" s="41" t="s">
         <v>305</v>
       </c>
-      <c r="B97" s="54" t="s">
+      <c r="B97" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="C97" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D97" s="55">
+      <c r="C97" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D97" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="53" t="s">
+      <c r="A98" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="B98" s="54" t="s">
+      <c r="B98" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="C98" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D98" s="55">
+      <c r="C98" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D98" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="53" t="s">
+      <c r="A99" s="41" t="s">
         <v>308</v>
       </c>
-      <c r="B99" s="54" t="s">
+      <c r="B99" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="C99" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D99" s="55">
+      <c r="C99" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D99" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="53" t="s">
+      <c r="A100" s="41" t="s">
         <v>310</v>
       </c>
-      <c r="B100" s="54" t="s">
+      <c r="B100" s="42" t="s">
         <v>311</v>
       </c>
-      <c r="C100" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D100" s="55">
+      <c r="C100" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D100" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="53" t="s">
+      <c r="A101" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="B101" s="54" t="s">
+      <c r="B101" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="C101" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D101" s="55">
+      <c r="C101" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D101" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="53" t="s">
+      <c r="A102" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="B102" s="54" t="s">
+      <c r="B102" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="C102" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D102" s="55">
+      <c r="C102" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D102" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="53" t="s">
+      <c r="A103" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="B103" s="54" t="s">
+      <c r="B103" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="C103" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D103" s="55">
+      <c r="C103" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D103" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="53" t="s">
+      <c r="A104" s="41" t="s">
         <v>317</v>
       </c>
-      <c r="B104" s="54" t="s">
+      <c r="B104" s="42" t="s">
         <v>318</v>
       </c>
-      <c r="C104" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D104" s="55">
+      <c r="C104" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D104" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="53" t="s">
+      <c r="A105" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B105" s="54" t="s">
+      <c r="B105" s="42" t="s">
         <v>319</v>
       </c>
-      <c r="C105" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D105" s="55">
+      <c r="C105" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D105" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="53" t="s">
+      <c r="A106" s="41" t="s">
         <v>320</v>
       </c>
-      <c r="B106" s="54" t="s">
+      <c r="B106" s="42" t="s">
         <v>321</v>
       </c>
-      <c r="C106" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D106" s="55">
+      <c r="C106" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D106" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="53" t="s">
+      <c r="A107" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="B107" s="54" t="s">
+      <c r="B107" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="C107" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D107" s="55">
+      <c r="C107" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D107" s="43">
         <v>0.26697408552192708</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="53" t="s">
+      <c r="A108" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="B108" s="54" t="s">
+      <c r="B108" s="42" t="s">
         <v>325</v>
       </c>
-      <c r="C108" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D108" s="55">
+      <c r="C108" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D108" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="53" t="s">
+      <c r="A109" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B109" s="54" t="s">
+      <c r="B109" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="C109" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D109" s="55">
+      <c r="C109" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D109" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="53" t="s">
+      <c r="A110" s="41" t="s">
         <v>328</v>
       </c>
-      <c r="B110" s="54" t="s">
+      <c r="B110" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="C110" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D110" s="55">
+      <c r="C110" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D110" s="43">
         <v>0.30979413994586297</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="53" t="s">
+      <c r="A111" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="B111" s="54" t="s">
+      <c r="B111" s="42" t="s">
         <v>331</v>
       </c>
-      <c r="C111" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D111" s="55">
+      <c r="C111" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D111" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="53" t="s">
+      <c r="A112" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="B112" s="54" t="s">
+      <c r="B112" s="42" t="s">
         <v>333</v>
       </c>
-      <c r="C112" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D112" s="55">
+      <c r="C112" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D112" s="43">
         <v>0.33945692747523504</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="53" t="s">
+      <c r="A113" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B113" s="54" t="s">
+      <c r="B113" s="42" t="s">
         <v>334</v>
       </c>
-      <c r="C113" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D113" s="55">
+      <c r="C113" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D113" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="53" t="s">
+      <c r="A114" s="41" t="s">
         <v>335</v>
       </c>
-      <c r="B114" s="54" t="s">
+      <c r="B114" s="42" t="s">
         <v>336</v>
       </c>
-      <c r="C114" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D114" s="55">
+      <c r="C114" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D114" s="43">
         <v>0.44764149344092746</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="53" t="s">
+      <c r="A115" s="41" t="s">
         <v>337</v>
       </c>
-      <c r="B115" s="54" t="s">
+      <c r="B115" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="C115" s="53" t="s">
+      <c r="C115" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D115" s="55">
+      <c r="D115" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="53" t="s">
+      <c r="A116" s="41" t="s">
         <v>339</v>
       </c>
-      <c r="B116" s="54" t="s">
+      <c r="B116" s="42" t="s">
         <v>340</v>
       </c>
-      <c r="C116" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D116" s="55">
+      <c r="C116" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D116" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="53" t="s">
+      <c r="A117" s="41" t="s">
         <v>341</v>
       </c>
-      <c r="B117" s="54" t="s">
+      <c r="B117" s="42" t="s">
         <v>342</v>
       </c>
-      <c r="C117" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D117" s="55">
+      <c r="C117" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D117" s="43">
         <v>0.28888497390074974</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="53" t="s">
+      <c r="A118" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="B118" s="54" t="s">
+      <c r="B118" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="C118" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D118" s="55">
+      <c r="C118" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D118" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="53" t="s">
+      <c r="A119" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="B119" s="54" t="s">
+      <c r="B119" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="C119" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D119" s="55">
+      <c r="C119" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D119" s="43">
         <v>0.29597714018653326</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="53" t="s">
+      <c r="A120" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="B120" s="54" t="s">
+      <c r="B120" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="C120" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D120" s="55">
+      <c r="C120" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D120" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="53" t="s">
+      <c r="A121" s="41" t="s">
         <v>349</v>
       </c>
-      <c r="B121" s="54" t="s">
+      <c r="B121" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="C121" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D121" s="55">
+      <c r="C121" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D121" s="43">
         <v>0.38649274668168621</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="53" t="s">
+      <c r="A122" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="B122" s="54" t="s">
+      <c r="B122" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="C122" s="53" t="s">
+      <c r="C122" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D122" s="55">
+      <c r="D122" s="43">
         <v>0.36578997821670428</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="53" t="s">
+      <c r="A123" s="41" t="s">
         <v>353</v>
       </c>
-      <c r="B123" s="54" t="s">
+      <c r="B123" s="42" t="s">
         <v>354</v>
       </c>
-      <c r="C123" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D123" s="55">
+      <c r="C123" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D123" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="53" t="s">
+      <c r="A124" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="B124" s="54" t="s">
+      <c r="B124" s="42" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D124" s="55">
+      <c r="C124" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D124" s="43">
         <v>0.35881075582858007</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="53" t="s">
+      <c r="A125" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="B125" s="54" t="s">
+      <c r="B125" s="42" t="s">
         <v>358</v>
       </c>
-      <c r="C125" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D125" s="55">
+      <c r="C125" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D125" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="53" t="s">
+      <c r="A126" s="41" t="s">
         <v>359</v>
       </c>
-      <c r="B126" s="54" t="s">
+      <c r="B126" s="42" t="s">
         <v>360</v>
       </c>
-      <c r="C126" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D126" s="55">
+      <c r="C126" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D126" s="43">
         <v>0.35189591990884583</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="53" t="s">
+      <c r="A127" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="B127" s="54" t="s">
+      <c r="B127" s="42" t="s">
         <v>362</v>
       </c>
-      <c r="C127" s="53" t="s">
+      <c r="C127" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D127" s="55">
+      <c r="D127" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="53" t="s">
+      <c r="A128" s="41" t="s">
         <v>363</v>
       </c>
-      <c r="B128" s="54" t="s">
+      <c r="B128" s="42" t="s">
         <v>364</v>
       </c>
-      <c r="C128" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D128" s="55">
+      <c r="C128" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D128" s="43">
         <v>0.351727634700162</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="53" t="s">
+      <c r="A129" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="B129" s="54" t="s">
+      <c r="B129" s="42" t="s">
         <v>366</v>
       </c>
-      <c r="C129" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D129" s="55">
+      <c r="C129" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D129" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="53" t="s">
+      <c r="A130" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B130" s="54" t="s">
+      <c r="B130" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="C130" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D130" s="55">
+      <c r="C130" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D130" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="53" t="s">
+      <c r="A131" s="41" t="s">
         <v>368</v>
       </c>
-      <c r="B131" s="54" t="s">
+      <c r="B131" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="C131" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D131" s="55">
+      <c r="C131" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D131" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="53" t="s">
+      <c r="A132" s="41" t="s">
         <v>370</v>
       </c>
-      <c r="B132" s="54" t="s">
+      <c r="B132" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="C132" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D132" s="55">
+      <c r="C132" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D132" s="43">
         <v>0.38431196686777208</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="53" t="s">
+      <c r="A133" s="41" t="s">
         <v>372</v>
       </c>
-      <c r="B133" s="54" t="s">
+      <c r="B133" s="42" t="s">
         <v>373</v>
       </c>
-      <c r="C133" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D133" s="55">
+      <c r="C133" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D133" s="43">
         <v>0.35393159014210485</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="53" t="s">
+      <c r="A134" s="41" t="s">
         <v>374</v>
       </c>
-      <c r="B134" s="54" t="s">
+      <c r="B134" s="42" t="s">
         <v>375</v>
       </c>
-      <c r="C134" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D134" s="55">
+      <c r="C134" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D134" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="53" t="s">
+      <c r="A135" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="B135" s="54" t="s">
+      <c r="B135" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="C135" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D135" s="55">
+      <c r="C135" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D135" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="53" t="s">
+      <c r="A136" s="41" t="s">
         <v>378</v>
       </c>
-      <c r="B136" s="54" t="s">
+      <c r="B136" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="C136" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D136" s="55">
+      <c r="C136" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D136" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="53" t="s">
+      <c r="A137" s="41" t="s">
         <v>380</v>
       </c>
-      <c r="B137" s="54" t="s">
+      <c r="B137" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="C137" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D137" s="55">
+      <c r="C137" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D137" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="53" t="s">
+      <c r="A138" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="B138" s="54" t="s">
+      <c r="B138" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="C138" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D138" s="55">
+      <c r="C138" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D138" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="53" t="s">
+      <c r="A139" s="41" t="s">
         <v>384</v>
       </c>
-      <c r="B139" s="54" t="s">
+      <c r="B139" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="C139" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D139" s="55">
+      <c r="C139" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D139" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="53" t="s">
+      <c r="A140" s="41" t="s">
         <v>386</v>
       </c>
-      <c r="B140" s="54" t="s">
+      <c r="B140" s="42" t="s">
         <v>387</v>
       </c>
-      <c r="C140" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D140" s="55">
+      <c r="C140" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D140" s="43">
         <v>0.35274244523672371</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="53" t="s">
+      <c r="A141" s="41" t="s">
         <v>388</v>
       </c>
-      <c r="B141" s="54" t="s">
+      <c r="B141" s="42" t="s">
         <v>389</v>
       </c>
-      <c r="C141" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D141" s="55">
+      <c r="C141" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D141" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="53" t="s">
+      <c r="A142" s="41" t="s">
         <v>390</v>
       </c>
-      <c r="B142" s="54" t="s">
+      <c r="B142" s="42" t="s">
         <v>391</v>
       </c>
-      <c r="C142" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D142" s="55">
+      <c r="C142" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D142" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="53" t="s">
+      <c r="A143" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="B143" s="54" t="s">
+      <c r="B143" s="42" t="s">
         <v>393</v>
       </c>
-      <c r="C143" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D143" s="55">
+      <c r="C143" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D143" s="43">
         <v>0.37179926680834124</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="53" t="s">
+      <c r="A144" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="B144" s="54" t="s">
+      <c r="B144" s="42" t="s">
         <v>395</v>
       </c>
-      <c r="C144" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D144" s="55">
+      <c r="C144" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D144" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="53" t="s">
+      <c r="A145" s="41" t="s">
         <v>396</v>
       </c>
-      <c r="B145" s="54" t="s">
+      <c r="B145" s="42" t="s">
         <v>397</v>
       </c>
-      <c r="C145" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D145" s="55">
+      <c r="C145" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D145" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="53" t="s">
+      <c r="A146" s="41" t="s">
         <v>398</v>
       </c>
-      <c r="B146" s="54" t="s">
+      <c r="B146" s="42" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="53" t="s">
+      <c r="C146" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D146" s="55">
+      <c r="D146" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="53" t="s">
+      <c r="A147" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="B147" s="54" t="s">
+      <c r="B147" s="42" t="s">
         <v>401</v>
       </c>
-      <c r="C147" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D147" s="55">
+      <c r="C147" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D147" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="53" t="s">
+      <c r="A148" s="41" t="s">
         <v>402</v>
       </c>
-      <c r="B148" s="54" t="s">
+      <c r="B148" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="C148" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D148" s="55">
+      <c r="C148" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D148" s="43">
         <v>0.35338867089148501</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="53" t="s">
+      <c r="A149" s="41" t="s">
         <v>404</v>
       </c>
-      <c r="B149" s="54" t="s">
+      <c r="B149" s="42" t="s">
         <v>405</v>
       </c>
-      <c r="C149" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D149" s="55">
+      <c r="C149" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D149" s="43">
         <v>0.28529269187089412</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="53" t="s">
+      <c r="A150" s="41" t="s">
         <v>406</v>
       </c>
-      <c r="B150" s="54" t="s">
+      <c r="B150" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="C150" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D150" s="55">
+      <c r="C150" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D150" s="43">
         <v>0.30087029015518946</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="53" t="s">
+      <c r="A151" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="B151" s="54" t="s">
+      <c r="B151" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="C151" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D151" s="55">
+      <c r="C151" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D151" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="53" t="s">
+      <c r="A152" s="41" t="s">
         <v>410</v>
       </c>
-      <c r="B152" s="54" t="s">
+      <c r="B152" s="42" t="s">
         <v>411</v>
       </c>
-      <c r="C152" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D152" s="55">
+      <c r="C152" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D152" s="43">
         <v>0.50838740568321339</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="53" t="s">
+      <c r="A153" s="41" t="s">
         <v>412</v>
       </c>
-      <c r="B153" s="54" t="s">
+      <c r="B153" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="C153" s="53" t="s">
+      <c r="C153" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D153" s="55">
+      <c r="D153" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="53" t="s">
+      <c r="A154" s="41" t="s">
         <v>414</v>
       </c>
-      <c r="B154" s="54" t="s">
+      <c r="B154" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="C154" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D154" s="55">
+      <c r="C154" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D154" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="53" t="s">
+      <c r="A155" s="41" t="s">
         <v>416</v>
       </c>
-      <c r="B155" s="54" t="s">
+      <c r="B155" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="C155" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D155" s="55">
+      <c r="C155" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D155" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="53" t="s">
+      <c r="A156" s="41" t="s">
         <v>418</v>
       </c>
-      <c r="B156" s="54" t="s">
+      <c r="B156" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="C156" s="53" t="s">
+      <c r="C156" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D156" s="55">
+      <c r="D156" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="53" t="s">
+      <c r="A157" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="B157" s="54" t="s">
+      <c r="B157" s="42" t="s">
         <v>421</v>
       </c>
-      <c r="C157" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D157" s="55">
+      <c r="C157" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D157" s="43">
         <v>0.31787149727911646</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="53" t="s">
+      <c r="A158" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="B158" s="54" t="s">
+      <c r="B158" s="42" t="s">
         <v>423</v>
       </c>
-      <c r="C158" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D158" s="55">
+      <c r="C158" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D158" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="53" t="s">
+      <c r="A159" s="41" t="s">
         <v>424</v>
       </c>
-      <c r="B159" s="54" t="s">
+      <c r="B159" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="C159" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D159" s="55">
+      <c r="C159" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D159" s="43">
         <v>1.5277121009144217</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="53" t="s">
+      <c r="A160" s="41" t="s">
         <v>426</v>
       </c>
-      <c r="B160" s="54" t="s">
+      <c r="B160" s="42" t="s">
         <v>427</v>
       </c>
-      <c r="C160" s="53" t="s">
+      <c r="C160" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D160" s="55">
+      <c r="D160" s="43">
         <v>0.30061760815337318</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="53" t="s">
+      <c r="A161" s="41" t="s">
         <v>428</v>
       </c>
-      <c r="B161" s="54" t="s">
+      <c r="B161" s="42" t="s">
         <v>429</v>
       </c>
-      <c r="C161" s="53" t="s">
+      <c r="C161" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D161" s="55">
+      <c r="D161" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="53" t="s">
+      <c r="A162" s="41" t="s">
         <v>430</v>
       </c>
-      <c r="B162" s="54" t="s">
+      <c r="B162" s="42" t="s">
         <v>431</v>
       </c>
-      <c r="C162" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D162" s="55">
+      <c r="C162" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D162" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="53" t="s">
+      <c r="A163" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B163" s="54" t="s">
+      <c r="B163" s="42" t="s">
         <v>432</v>
       </c>
-      <c r="C163" s="53" t="s">
+      <c r="C163" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D163" s="55">
+      <c r="D163" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="53" t="s">
+      <c r="A164" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="B164" s="54" t="s">
+      <c r="B164" s="42" t="s">
         <v>433</v>
       </c>
-      <c r="C164" s="53" t="s">
+      <c r="C164" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D164" s="55">
+      <c r="D164" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="53" t="s">
+      <c r="A165" s="41" t="s">
         <v>434</v>
       </c>
-      <c r="B165" s="54" t="s">
+      <c r="B165" s="42" t="s">
         <v>435</v>
       </c>
-      <c r="C165" s="53" t="s">
+      <c r="C165" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D165" s="55">
+      <c r="D165" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="53" t="s">
+      <c r="A166" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B166" s="54" t="s">
+      <c r="B166" s="42" t="s">
         <v>436</v>
       </c>
-      <c r="C166" s="53" t="s">
+      <c r="C166" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D166" s="55">
+      <c r="D166" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="53" t="s">
+      <c r="A167" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B167" s="54" t="s">
+      <c r="B167" s="42" t="s">
         <v>437</v>
       </c>
-      <c r="C167" s="53" t="s">
+      <c r="C167" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D167" s="55">
+      <c r="D167" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="53" t="s">
+      <c r="A168" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B168" s="54" t="s">
+      <c r="B168" s="42" t="s">
         <v>438</v>
       </c>
-      <c r="C168" s="53" t="s">
+      <c r="C168" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D168" s="55">
+      <c r="D168" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="53" t="s">
+      <c r="A169" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B169" s="54" t="s">
+      <c r="B169" s="42" t="s">
         <v>439</v>
       </c>
-      <c r="C169" s="53" t="s">
+      <c r="C169" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D169" s="55">
+      <c r="D169" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="53" t="s">
+      <c r="A170" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B170" s="54" t="s">
+      <c r="B170" s="42" t="s">
         <v>440</v>
       </c>
-      <c r="C170" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D170" s="55">
+      <c r="C170" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D170" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="53" t="s">
+      <c r="A171" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B171" s="54" t="s">
+      <c r="B171" s="42" t="s">
         <v>441</v>
       </c>
-      <c r="C171" s="53" t="s">
+      <c r="C171" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D171" s="55">
+      <c r="D171" s="43">
         <v>0.36813419592435975</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="53" t="s">
+      <c r="A172" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B172" s="54" t="s">
+      <c r="B172" s="42" t="s">
         <v>442</v>
       </c>
-      <c r="C172" s="53" t="s">
+      <c r="C172" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D172" s="55">
+      <c r="D172" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="53" t="s">
+      <c r="A173" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B173" s="54" t="s">
+      <c r="B173" s="42" t="s">
         <v>443</v>
       </c>
-      <c r="C173" s="53" t="s">
+      <c r="C173" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D173" s="55">
+      <c r="D173" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="53" t="s">
+      <c r="A174" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B174" s="54" t="s">
+      <c r="B174" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="C174" s="53" t="s">
+      <c r="C174" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D174" s="55">
+      <c r="D174" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="53" t="s">
+      <c r="A175" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B175" s="54" t="s">
+      <c r="B175" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="C175" s="53" t="s">
+      <c r="C175" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D175" s="55">
+      <c r="D175" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="53" t="s">
+      <c r="A176" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B176" s="54" t="s">
+      <c r="B176" s="42" t="s">
         <v>446</v>
       </c>
-      <c r="C176" s="53" t="s">
+      <c r="C176" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D176" s="55">
+      <c r="D176" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="53" t="s">
+      <c r="A177" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B177" s="54" t="s">
+      <c r="B177" s="42" t="s">
         <v>447</v>
       </c>
-      <c r="C177" s="53" t="s">
+      <c r="C177" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D177" s="55"/>
+      <c r="D177" s="43"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="53" t="s">
+      <c r="A178" s="41" t="s">
         <v>448</v>
       </c>
-      <c r="B178" s="54" t="s">
+      <c r="B178" s="42" t="s">
         <v>449</v>
       </c>
-      <c r="C178" s="53" t="s">
+      <c r="C178" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D178" s="55">
+      <c r="D178" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="53" t="s">
+      <c r="A179" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="B179" s="54" t="s">
+      <c r="B179" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="C179" s="53" t="s">
+      <c r="C179" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="D179" s="55"/>
+      <c r="D179" s="43"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="53" t="s">
+      <c r="A180" s="41" t="s">
         <v>452</v>
       </c>
-      <c r="B180" s="54" t="s">
+      <c r="B180" s="42" t="s">
         <v>453</v>
       </c>
-      <c r="C180" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D180" s="55">
+      <c r="C180" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D180" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="53" t="s">
+      <c r="A181" s="41" t="s">
         <v>454</v>
       </c>
-      <c r="B181" s="54" t="s">
+      <c r="B181" s="42" t="s">
         <v>455</v>
       </c>
-      <c r="C181" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D181" s="55">
+      <c r="C181" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D181" s="43">
         <v>0.54014095096644221</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="53" t="s">
+      <c r="A182" s="41" t="s">
         <v>456</v>
       </c>
-      <c r="B182" s="54" t="s">
+      <c r="B182" s="42" t="s">
         <v>457</v>
       </c>
-      <c r="C182" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D182" s="55">
+      <c r="C182" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D182" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="53" t="s">
+      <c r="A183" s="41" t="s">
         <v>458</v>
       </c>
-      <c r="B183" s="54" t="s">
+      <c r="B183" s="42" t="s">
         <v>459</v>
       </c>
-      <c r="C183" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D183" s="55">
+      <c r="C183" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D183" s="43">
         <v>0.35274244523672382</v>
       </c>
     </row>
@@ -7243,51 +7179,51 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.33203125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="1" max="1" width="26.33203125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14" style="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="7" width="11.44140625" style="11"/>
-    <col min="8" max="8" width="28.33203125" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="11.44140625" style="11"/>
+    <col min="5" max="7" width="11.44140625" style="10"/>
+    <col min="8" max="8" width="28.33203125" style="10" customWidth="1"/>
+    <col min="9" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="130" t="s">
         <v>461</v>
       </c>
-      <c r="B1" s="127"/>
+      <c r="B1" s="130"/>
     </row>
     <row r="2" spans="1:8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="44" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="45" t="s">
         <v>462</v>
       </c>
       <c r="B3" s="8">
         <v>2</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="46" t="s">
         <v>463</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="128" t="s">
+      <c r="C5" s="131" t="s">
         <v>460</v>
       </c>
-      <c r="D5" s="128"/>
+      <c r="D5" s="131"/>
       <c r="E5" s="6" t="s">
         <v>70</v>
       </c>
@@ -7296,98 +7232,98 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="25" t="s">
         <v>464</v>
       </c>
       <c r="C6" s="129" t="s">
         <v>465</v>
       </c>
       <c r="D6" s="129"/>
-      <c r="E6" s="32">
+      <c r="E6" s="26">
         <v>42736</v>
       </c>
-      <c r="F6" s="33"/>
-      <c r="H6" s="78" t="s">
+      <c r="F6" s="27"/>
+      <c r="H6" s="66" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="30" t="s">
         <v>503</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="25" t="s">
         <v>466</v>
       </c>
       <c r="C7" s="129" t="s">
         <v>465</v>
       </c>
       <c r="D7" s="129"/>
-      <c r="E7" s="32">
+      <c r="E7" s="26">
         <v>42736</v>
       </c>
-      <c r="F7" s="33"/>
-      <c r="H7" s="78" t="s">
+      <c r="F7" s="27"/>
+      <c r="H7" s="66" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="30" t="s">
         <v>506</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="25" t="s">
         <v>107</v>
       </c>
       <c r="C8" s="129">
         <v>0</v>
       </c>
       <c r="D8" s="129"/>
-      <c r="E8" s="32">
+      <c r="E8" s="26">
         <v>42736</v>
       </c>
-      <c r="F8" s="33"/>
-      <c r="H8" s="78" t="s">
+      <c r="F8" s="27"/>
+      <c r="H8" s="66" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="61" t="s">
         <v>505</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="60" t="s">
         <v>467</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="47" t="s">
         <v>468</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="26">
         <v>42736</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="H9" s="78" t="s">
+      <c r="F9" s="27"/>
+      <c r="H9" s="66" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="30" t="s">
         <v>504</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="25" t="s">
         <v>470</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="129" t="s">
         <v>465</v>
       </c>
-      <c r="D10" s="126"/>
-      <c r="E10" s="32">
+      <c r="D10" s="129"/>
+      <c r="E10" s="26">
         <v>42736</v>
       </c>
-      <c r="F10" s="33"/>
+      <c r="F10" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7408,20 +7344,20 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="59.88671875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="11"/>
-    <col min="6" max="6" width="78.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="27.88671875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="59.88671875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="10"/>
+    <col min="6" max="6" width="78.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="132" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="130"/>
+      <c r="B1" s="132"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
@@ -7441,121 +7377,121 @@
     </row>
     <row r="4" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="48" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+      <c r="A6" s="21">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="22" t="s">
         <v>473</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="49">
         <v>42736</v>
       </c>
-      <c r="D6" s="62"/>
-      <c r="F6" s="11" t="s">
+      <c r="D6" s="50"/>
+      <c r="F6" s="10" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="21">
         <v>2</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="38">
         <v>42736</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="24"/>
+      <c r="F7" s="10" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+      <c r="A8" s="21">
         <v>3</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="38">
         <v>42736</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="F8" s="11" t="s">
+      <c r="D8" s="24"/>
+      <c r="F8" s="10" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="21">
         <v>4</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="38">
         <v>42736</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="F9" s="11" t="s">
+      <c r="D9" s="24"/>
+      <c r="F9" s="10" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="A10" s="21">
         <v>5</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="22" t="s">
         <v>477</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="38">
         <v>42736</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="F10" s="11" t="s">
+      <c r="D10" s="24"/>
+      <c r="F10" s="10" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
+      <c r="A11" s="21">
         <v>6</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="38">
         <v>42736</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="F11" s="11" t="s">
+      <c r="D11" s="24"/>
+      <c r="F11" s="10" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
+      <c r="A12" s="21">
         <v>7</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="38">
         <v>42943</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="F12" s="11" t="s">
+      <c r="D12" s="24"/>
+      <c r="F12" s="10" t="s">
         <v>556</v>
       </c>
     </row>
@@ -7573,21 +7509,21 @@
   <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.33203125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="94.33203125" style="11" customWidth="1"/>
-    <col min="3" max="4" width="16.6640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17" style="11" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="11"/>
-    <col min="8" max="8" width="116.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="26.33203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="94.33203125" style="10" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="17" style="10" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="10"/>
+    <col min="8" max="8" width="116.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.44140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="133" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="131"/>
+      <c r="B1" s="133"/>
     </row>
     <row r="2" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -7606,500 +7542,500 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="134" t="s">
         <v>481</v>
       </c>
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="136" t="s">
+      <c r="C5" s="138" t="s">
         <v>482</v>
       </c>
-      <c r="D5" s="136"/>
-      <c r="E5" s="137" t="s">
+      <c r="D5" s="138"/>
+      <c r="E5" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="137" t="s">
+      <c r="F5" s="139" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="133"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="135"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="55" t="s">
         <v>483</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="55" t="s">
         <v>484</v>
       </c>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="57" t="s">
         <v>507</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="26">
         <v>42736</v>
       </c>
-      <c r="F7" s="33"/>
-      <c r="H7" s="11" t="s">
+      <c r="F7" s="27"/>
+      <c r="H7" s="10" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="26">
         <v>42736</v>
       </c>
-      <c r="F8" s="33"/>
-      <c r="H8" s="11" t="s">
+      <c r="F8" s="27"/>
+      <c r="H8" s="10" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="41" t="s">
         <v>486</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="42" t="s">
         <v>509</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="26">
         <v>42736</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="H9" s="11" t="s">
+      <c r="F9" s="27"/>
+      <c r="H9" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="41" t="s">
         <v>487</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="42" t="s">
         <v>510</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="26">
         <v>42736</v>
       </c>
-      <c r="F10" s="33"/>
-      <c r="H10" s="11" t="s">
+      <c r="F10" s="27"/>
+      <c r="H10" s="10" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="41" t="s">
         <v>488</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="42" t="s">
         <v>511</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="26">
         <v>42736</v>
       </c>
-      <c r="F11" s="33"/>
-      <c r="H11" s="11" t="s">
+      <c r="F11" s="27"/>
+      <c r="H11" s="10" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="42" t="s">
         <v>512</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="26">
         <v>42736</v>
       </c>
-      <c r="F12" s="33"/>
-      <c r="H12" s="11" t="s">
+      <c r="F12" s="27"/>
+      <c r="H12" s="10" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="41" t="s">
         <v>490</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="42" t="s">
         <v>513</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="26">
         <v>42736</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="H13" s="11" t="s">
+      <c r="F13" s="27"/>
+      <c r="H13" s="10" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="42" t="s">
         <v>514</v>
       </c>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="26">
         <v>42736</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="H14" s="11" t="s">
+      <c r="F14" s="27"/>
+      <c r="H14" s="10" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="41" t="s">
         <v>492</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="42" t="s">
         <v>515</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="71" t="s">
+      <c r="D15" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="26">
         <v>42736</v>
       </c>
-      <c r="F15" s="33"/>
-      <c r="H15" s="11" t="s">
+      <c r="F15" s="27"/>
+      <c r="H15" s="10" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="41" t="s">
         <v>493</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="42" t="s">
         <v>516</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="26">
         <v>42736</v>
       </c>
-      <c r="F16" s="33"/>
-      <c r="H16" s="11" t="s">
+      <c r="F16" s="27"/>
+      <c r="H16" s="10" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="26">
         <v>42736</v>
       </c>
-      <c r="F17" s="33"/>
-      <c r="H17" s="11" t="s">
+      <c r="F17" s="27"/>
+      <c r="H17" s="10" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="41" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="42" t="s">
         <v>518</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="26">
         <v>42736</v>
       </c>
-      <c r="F18" s="33"/>
-      <c r="H18" s="11" t="s">
+      <c r="F18" s="27"/>
+      <c r="H18" s="10" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="41" t="s">
         <v>496</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="42" t="s">
         <v>519</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="26">
         <v>42736</v>
       </c>
-      <c r="F19" s="33"/>
-      <c r="H19" s="11" t="s">
+      <c r="F19" s="27"/>
+      <c r="H19" s="10" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="42" t="s">
         <v>520</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="26">
         <v>42736</v>
       </c>
-      <c r="F20" s="33"/>
-      <c r="H20" s="11" t="s">
+      <c r="F20" s="27"/>
+      <c r="H20" s="10" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="42" t="s">
         <v>521</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="D21" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="26">
         <v>42736</v>
       </c>
-      <c r="F21" s="33"/>
-      <c r="H21" s="11" t="s">
+      <c r="F21" s="27"/>
+      <c r="H21" s="10" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="41" t="s">
         <v>497</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="42" t="s">
         <v>522</v>
       </c>
-      <c r="C22" s="71" t="s">
+      <c r="C22" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="71" t="s">
+      <c r="D22" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="26">
         <v>42736</v>
       </c>
-      <c r="F22" s="33"/>
-      <c r="H22" s="11" t="s">
+      <c r="F22" s="27"/>
+      <c r="H22" s="10" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="41" t="s">
         <v>498</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="D23" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="26">
         <v>42736</v>
       </c>
-      <c r="F23" s="33"/>
-      <c r="H23" s="11" t="s">
+      <c r="F23" s="27"/>
+      <c r="H23" s="10" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="41" t="s">
         <v>499</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="42" t="s">
         <v>524</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="26">
         <v>42736</v>
       </c>
-      <c r="F24" s="33"/>
-      <c r="H24" s="11" t="s">
+      <c r="F24" s="27"/>
+      <c r="H24" s="10" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="41" t="s">
         <v>500</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="42" t="s">
         <v>525</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="26">
         <v>42736</v>
       </c>
-      <c r="F25" s="33"/>
-      <c r="H25" s="11" t="s">
+      <c r="F25" s="27"/>
+      <c r="H25" s="10" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="41" t="s">
         <v>501</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="42" t="s">
         <v>526</v>
       </c>
-      <c r="C26" s="71" t="s">
+      <c r="C26" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="26">
         <v>42736</v>
       </c>
-      <c r="F26" s="33"/>
-      <c r="H26" s="11" t="s">
+      <c r="F26" s="27"/>
+      <c r="H26" s="10" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="C27" s="71" t="s">
+      <c r="C27" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="26">
         <v>42736</v>
       </c>
-      <c r="F27" s="33"/>
-      <c r="H27" s="11" t="s">
+      <c r="F27" s="27"/>
+      <c r="H27" s="10" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="41" t="s">
         <v>502</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="42" t="s">
         <v>528</v>
       </c>
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="26">
         <v>42825</v>
       </c>
-      <c r="F28" s="33"/>
-      <c r="H28" s="11" t="s">
+      <c r="F28" s="27"/>
+      <c r="H28" s="10" t="s">
         <v>549</v>
       </c>
     </row>
@@ -8131,12 +8067,12 @@
     <row r="125" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8149,15 +8085,15 @@
   <cols>
     <col min="1" max="1" width="2.109375" customWidth="1"/>
     <col min="2" max="2" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" style="89" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="89" customWidth="1"/>
-    <col min="5" max="5" width="29.33203125" style="89" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" style="89" customWidth="1"/>
-    <col min="7" max="7" width="55.5546875" style="89" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" style="89" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" style="89" customWidth="1"/>
-    <col min="11" max="11" width="20" style="89" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="55.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20" style="2" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" customWidth="1"/>
     <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
@@ -8166,327 +8102,316 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="96"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
     </row>
     <row r="2" spans="2:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="94"/>
-      <c r="C2" s="94" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79" t="s">
         <v>591</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="112" t="s">
         <v>602</v>
       </c>
-      <c r="E2" s="140"/>
-      <c r="F2" s="141"/>
-      <c r="H2" s="89" t="s">
+      <c r="E2" s="113"/>
+      <c r="F2" s="114"/>
+      <c r="H2" s="2" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="144"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="148"/>
-      <c r="L3" s="148"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="117"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
     </row>
     <row r="4" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="149" t="s">
+      <c r="B4" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="149"/>
-      <c r="D4" s="145"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="147"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="150"/>
-      <c r="L4" s="150"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="120"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
     </row>
     <row r="5" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="150"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
     </row>
     <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="151" t="s">
+      <c r="C6" s="76"/>
+      <c r="D6" s="123" t="s">
         <v>604</v>
       </c>
-      <c r="E6" s="152"/>
+      <c r="E6" s="124"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="150"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="150"/>
-      <c r="L6" s="150"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
     </row>
     <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="101"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="156" t="s">
+      <c r="B8" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="156"/>
-      <c r="D8" s="103" t="s">
+      <c r="C8" s="103"/>
+      <c r="D8" s="88" t="s">
         <v>605</v>
       </c>
-      <c r="E8" s="95"/>
-      <c r="F8" s="107" t="s">
+      <c r="E8" s="80"/>
+      <c r="F8" s="91" t="s">
         <v>590</v>
       </c>
-      <c r="G8" s="74"/>
-      <c r="H8" s="76"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="64"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="156" t="s">
+      <c r="B9" s="103" t="s">
         <v>583</v>
       </c>
-      <c r="C9" s="156"/>
-      <c r="D9" s="117" t="s">
+      <c r="C9" s="103"/>
+      <c r="D9" s="99" t="s">
         <v>607</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="107" t="s">
+      <c r="E9" s="80"/>
+      <c r="F9" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="62" t="s">
         <v>558</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="155"/>
-      <c r="J9" s="155"/>
-      <c r="K9" s="84" t="s">
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="72" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="156" t="s">
+      <c r="B10" s="103" t="s">
         <v>584</v>
       </c>
-      <c r="C10" s="156"/>
-      <c r="D10" s="108" t="s">
+      <c r="C10" s="103"/>
+      <c r="D10" s="92" t="s">
         <v>608</v>
       </c>
-      <c r="E10" s="95"/>
-      <c r="F10" s="107" t="s">
+      <c r="E10" s="80"/>
+      <c r="F10" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="75"/>
+      <c r="G10" s="63"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="155"/>
-      <c r="J10" s="155"/>
-      <c r="K10" s="84" t="s">
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="72" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="98" t="s">
         <v>585</v>
       </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="118" t="s">
+      <c r="C11" s="98"/>
+      <c r="D11" s="100" t="s">
         <v>609</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="107" t="s">
+      <c r="E11" s="80"/>
+      <c r="F11" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="62" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="156" t="s">
+      <c r="B12" s="103" t="s">
         <v>586</v>
       </c>
-      <c r="C12" s="156"/>
-      <c r="D12" s="118" t="s">
+      <c r="C12" s="103"/>
+      <c r="D12" s="100" t="s">
         <v>610</v>
       </c>
-      <c r="E12" s="95"/>
-      <c r="F12" s="107" t="s">
+      <c r="E12" s="80"/>
+      <c r="F12" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="74" t="s">
+      <c r="G12" s="62" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="156" t="s">
+      <c r="B13" s="103" t="s">
         <v>587</v>
       </c>
-      <c r="C13" s="156"/>
-      <c r="D13" s="108" t="s">
+      <c r="C13" s="103"/>
+      <c r="D13" s="92" t="s">
         <v>606</v>
       </c>
-      <c r="E13" s="95"/>
-      <c r="F13" s="109" t="s">
+      <c r="E13" s="80"/>
+      <c r="F13" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="83" t="s">
+      <c r="G13" s="71" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="89" t="s">
         <v>597</v>
       </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="108" t="s">
+      <c r="C14" s="90"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="92" t="s">
         <v>601</v>
       </c>
-      <c r="F14" s="103"/>
+      <c r="F14" s="88"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="157" t="s">
+      <c r="B16" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="157"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="100" t="s">
+      <c r="C16" s="104"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="100"/>
-      <c r="I16" s="159"/>
-      <c r="J16" s="159"/>
-      <c r="K16" s="160"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="107"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="161" t="s">
+      <c r="B18" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="161"/>
-      <c r="D18" s="161"/>
-      <c r="E18" s="161"/>
-      <c r="F18" s="161"/>
-      <c r="G18" s="161"/>
-      <c r="H18" s="161"/>
-      <c r="I18" s="161"/>
-      <c r="J18" s="161"/>
-      <c r="K18" s="161"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="108"/>
     </row>
     <row r="19" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="99" t="s">
+      <c r="D19" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="111" t="s">
+      <c r="E19" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="99" t="s">
+      <c r="F19" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="99" t="s">
+      <c r="G19" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="114" t="s">
+      <c r="H19" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="154" t="s">
+      <c r="I19" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="154"/>
-      <c r="K19" s="99" t="s">
+      <c r="J19" s="110"/>
+      <c r="K19" s="84" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="85">
+      <c r="B20" s="73">
         <v>1</v>
       </c>
-      <c r="C20" s="119">
+      <c r="C20" s="101">
         <v>78181500</v>
       </c>
-      <c r="D20" s="106">
+      <c r="D20" s="74">
         <v>3</v>
       </c>
-      <c r="E20" s="112" t="s">
+      <c r="E20" s="95" t="s">
         <v>599</v>
       </c>
-      <c r="F20" s="106" t="s">
+      <c r="F20" s="74" t="s">
         <v>600</v>
       </c>
-      <c r="G20" s="120" t="s">
+      <c r="G20" s="102" t="s">
         <v>603</v>
       </c>
-      <c r="H20" s="115">
+      <c r="H20" s="97">
         <f>132500/1.16/D20</f>
         <v>38074.712643678162</v>
       </c>
-      <c r="I20" s="86" t="s">
+      <c r="I20" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="87">
+      <c r="J20" s="75">
         <f>(D20*H20)*0.16</f>
         <v>18275.862068965518</v>
       </c>
-      <c r="K20" s="88">
+      <c r="K20" s="75">
         <f>(D20*H20)</f>
         <v>114224.13793103449</v>
       </c>
-      <c r="N20" s="98"/>
-      <c r="O20" s="113">
-        <v>31030</v>
-      </c>
+      <c r="N20" s="83"/>
+      <c r="O20" s="96"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="2"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="153" t="s">
+      <c r="I22" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="J22" s="153"/>
+      <c r="J22" s="109"/>
       <c r="K22" s="5">
         <f>SUM(K20:K20)</f>
         <v>114224.13793103449</v>
@@ -8494,16 +8419,11 @@
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="153" t="s">
+      <c r="I23" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="153"/>
+      <c r="J23" s="109"/>
       <c r="K23" s="5">
         <f>SUM(J20:J20)</f>
         <v>18275.862068965518</v>
@@ -8511,57 +8431,52 @@
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="153" t="s">
+      <c r="I24" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="J24" s="153"/>
+      <c r="J24" s="109"/>
       <c r="K24" s="5">
         <f>K22+K23</f>
         <v>132500</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E25" s="90"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E26" s="90"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E27" s="90"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E28" s="90"/>
+      <c r="E28" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="D2:F4"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I22:J22"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D2:F4"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:L6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G13:G14" xr:uid="{B759EEAB-8083-40F1-B873-759D27CF6E74}">
@@ -8594,7 +8509,7 @@
   </cols>
   <sheetData>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="103">
+      <c r="A7" s="88">
         <v>1</v>
       </c>
       <c r="B7" t="s">
@@ -8602,7 +8517,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="103">
+      <c r="A8" s="88">
         <v>2</v>
       </c>
       <c r="B8" t="s">
@@ -8610,7 +8525,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="103">
+      <c r="A9" s="88">
         <v>3</v>
       </c>
       <c r="B9" t="s">
@@ -8618,7 +8533,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="103">
+      <c r="A10" s="88">
         <v>4</v>
       </c>
       <c r="B10" t="s">
@@ -8626,15 +8541,15 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="103">
+      <c r="A11" s="88">
         <v>5</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="87" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
+      <c r="A12" s="88"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
